--- a/bus_booking.xlsx
+++ b/bus_booking.xlsx
@@ -8,18 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\front2\OneDrive\ドキュメント\bus-booking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA87738A-D4C1-4B4C-9428-CB9ABB978F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFDAB55-9B92-4FF0-849E-B2F982AF3C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{EED53E60-892A-4A6C-956D-BF49B55530D5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EED53E60-892A-4A6C-956D-BF49B55530D5}"/>
   </bookViews>
   <sheets>
-    <sheet name="070426~(2)" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="print" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="print" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'070426~(2)'!$A$1:$D$41</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">print!$B$1:$D$44,print!$F$1:$I$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">print!$B$1:$D$44,print!$F$1:$I$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>月　　　　日   　　(　　　)</t>
     <rPh sb="0" eb="1">
@@ -64,9 +62,6 @@
   <si>
     <t>9:30</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>8:30</t>
   </si>
   <si>
     <t>10:00</t>
@@ -136,7 +131,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,15 +175,6 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
@@ -214,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -238,43 +224,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -648,7 +597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -656,142 +605,108 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1073,312 +988,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F66E9A18-76DC-4C7F-B0C0-534235C6840A}">
-  <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="1" max="1" width="7.625" customWidth="1"/>
-    <col min="2" max="2" width="53.625" customWidth="1"/>
-    <col min="3" max="3" width="7.625" customWidth="1"/>
-    <col min="4" max="4" width="53.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="25.5">
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="9.75" customHeight="1" thickBot="1">
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A4" s="45"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A5" s="45"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A7" s="45"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A8" s="45"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A9" s="45"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A10" s="45"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A11" s="45"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A12" s="45"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A13" s="45"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A14" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="10"/>
-    </row>
-    <row r="15" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A15" s="49"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A16" s="49"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="17" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A17" s="49"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="11"/>
-    </row>
-    <row r="18" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A18" s="49"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="11"/>
-    </row>
-    <row r="19" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="11"/>
-    </row>
-    <row r="20" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A20" s="49"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="11"/>
-    </row>
-    <row r="21" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A21" s="49"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A22" s="49"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A23" s="49"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A24" s="49"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="12"/>
-    </row>
-    <row r="25" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A25" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="11"/>
-    </row>
-    <row r="26" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A26" s="49"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="11"/>
-    </row>
-    <row r="27" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A27" s="49"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="11"/>
-    </row>
-    <row r="28" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="11"/>
-    </row>
-    <row r="29" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A29" s="49"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="11"/>
-    </row>
-    <row r="30" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A30" s="49"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="11"/>
-    </row>
-    <row r="31" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A31" s="49"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="11"/>
-    </row>
-    <row r="32" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A32" s="49"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="11"/>
-    </row>
-    <row r="33" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A33" s="49"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="11"/>
-    </row>
-    <row r="34" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A34" s="49"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="11"/>
-    </row>
-    <row r="35" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A35" s="49"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="11"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="50"/>
-      <c r="B36" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="35"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="50"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="37"/>
-    </row>
-    <row r="38" spans="1:4" ht="24" customHeight="1">
-      <c r="A38" s="50"/>
-      <c r="B38" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="39"/>
-    </row>
-    <row r="39" spans="1:4" ht="24" customHeight="1">
-      <c r="A39" s="50"/>
-      <c r="B39" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="41"/>
-    </row>
-    <row r="40" spans="1:4" ht="24" customHeight="1">
-      <c r="A40" s="50"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="41"/>
-    </row>
-    <row r="41" spans="1:4" ht="19.5" thickBot="1">
-      <c r="A41" s="51"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="43"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="D43" s="18"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="A3:A13"/>
-    <mergeCell ref="C3:C13"/>
-    <mergeCell ref="A14:A24"/>
-    <mergeCell ref="C14:C24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="C25:C35"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="67" orientation="portrait" r:id="rId1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="41" max="16383" man="1"/>
-  </rowBreaks>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="5" max="1048575" man="1"/>
-  </colBreaks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C007A4-FB0C-460B-8A76-612E291B3C94}">
   <dimension ref="B1:D44"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1388,7 +997,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="24">
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1396,226 +1005,226 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="2:4" ht="24.95" customHeight="1">
-      <c r="B3" s="20"/>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="4" spans="2:4" ht="10.5" customHeight="1">
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="50">
+      <c r="B5" s="23">
         <v>0.25347222222222221</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="50"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="50"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="50"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="50"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="50"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="50"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="50"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="50"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="50"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="50">
+      <c r="B15" s="23">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="50"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="50"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="50"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="50"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="50"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="50"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="50"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="50"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="50"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="31"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="50">
+      <c r="B25" s="23">
         <v>0.27777777777777779</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="50"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="50"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="50"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="50"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="29"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="50"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="50"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="29"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="50"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
     </row>
     <row r="33" spans="2:4">
-      <c r="B33" s="50"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="29"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="50"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="31"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="50">
+      <c r="B35" s="23">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="27"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="50"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="50"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="29"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="18"/>
     </row>
     <row r="38" spans="2:4">
-      <c r="B38" s="50"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="29"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="18"/>
     </row>
     <row r="39" spans="2:4">
-      <c r="B39" s="50"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="29"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="18"/>
     </row>
     <row r="40" spans="2:4">
-      <c r="B40" s="50"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="29"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18"/>
     </row>
     <row r="41" spans="2:4">
-      <c r="B41" s="50"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="29"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="18"/>
     </row>
     <row r="42" spans="2:4">
-      <c r="B42" s="50"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="29"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="18"/>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="50"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="29"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="18"/>
     </row>
     <row r="44" spans="2:4" ht="19.5" thickBot="1">
-      <c r="B44" s="51"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="33"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1630,7 +1239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF8E9232-62D3-4B7F-B723-39954B0A9115}">
   <dimension ref="B1:I47"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1645,7 +1254,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="25.5">
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1657,416 +1266,416 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="2:9" ht="24" customHeight="1">
-      <c r="B3" s="20"/>
-      <c r="C3" s="61" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="F3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B4" s="12"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="33"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B5" s="23">
+        <v>0.25347222222222221</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B6" s="23"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B7" s="23"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B8" s="23"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B9" s="23"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B10" s="23"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B11" s="23"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B12" s="23"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B13" s="23"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B15" s="23">
+        <v>0.2638888888888889</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="F15" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B16" s="23"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B17" s="23"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B18" s="23"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B19" s="23"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B20" s="23"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B21" s="23"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B22" s="23"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B23" s="23"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B24" s="23"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B25" s="23">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B26" s="23"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B27" s="23"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="F27" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="60" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="13"/>
-    </row>
-    <row r="4" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B4" s="23"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="64"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B5" s="50">
-        <v>0.25347222222222221</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B6" s="50"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B7" s="50"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B8" s="50"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B9" s="50"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B10" s="50"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B11" s="50"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B12" s="50"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B13" s="50"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B14" s="50"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="30"/>
-    </row>
-    <row r="15" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B15" s="50">
-        <v>0.2638888888888889</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="27"/>
-      <c r="F15" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B16" s="50"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B17" s="50"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B18" s="50"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B19" s="50"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B20" s="50"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B21" s="50"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B22" s="50"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B23" s="50"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B24" s="50"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="31"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B25" s="50">
-        <v>0.27777777777777779</v>
-      </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B26" s="50"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="30"/>
-    </row>
-    <row r="27" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B27" s="50"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="F27" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="59" t="s">
+      <c r="G27" s="4"/>
+      <c r="H27" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B28" s="23"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B29" s="23"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B30" s="23"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B31" s="23"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B32" s="23"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B33" s="23"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B34" s="23"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B35" s="23">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B36" s="23"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B37" s="23"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="18"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="23"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="18"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="19"/>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" s="23"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="18"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="13"/>
-    </row>
-    <row r="28" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B28" s="50"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="14"/>
-    </row>
-    <row r="29" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B29" s="50"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="29"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="14"/>
-    </row>
-    <row r="30" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B30" s="50"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="14"/>
-    </row>
-    <row r="31" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B31" s="50"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="29"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B32" s="50"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="14"/>
-    </row>
-    <row r="33" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B33" s="50"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="29"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="14"/>
-    </row>
-    <row r="34" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B34" s="50"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="31"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="14"/>
-    </row>
-    <row r="35" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B35" s="50">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="27"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="14"/>
-    </row>
-    <row r="36" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B36" s="50"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="14"/>
-    </row>
-    <row r="37" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B37" s="50"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="29"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="14"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="50"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="29"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="30"/>
-    </row>
-    <row r="39" spans="2:9">
-      <c r="B39" s="50"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="29"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="54" t="s">
+      <c r="H39" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="H39" s="34" t="s">
-        <v>8</v>
-      </c>
       <c r="I39" s="35"/>
     </row>
     <row r="40" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B40" s="50"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="29"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="54"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="44"/>
       <c r="H40" s="36"/>
       <c r="I40" s="37"/>
     </row>
     <row r="41" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B41" s="50"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="29"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="16" t="s">
+      <c r="B41" s="23"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="18"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="38" t="s">
+      <c r="I41" s="39"/>
+    </row>
+    <row r="42" spans="2:9" ht="18.75" customHeight="1">
+      <c r="B42" s="23"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="18"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="I41" s="39"/>
-    </row>
-    <row r="42" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B42" s="50"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="29"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="16" t="s">
-        <v>11</v>
       </c>
       <c r="H42" s="40"/>
       <c r="I42" s="41"/>
     </row>
     <row r="43" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B43" s="50"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="29"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="5"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="18"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I43" s="41"/>
     </row>
     <row r="44" spans="2:9" ht="19.5" thickBot="1">
-      <c r="B44" s="51"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="33"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="17"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="22"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="7"/>
       <c r="H44" s="42"/>
       <c r="I44" s="43"/>
     </row>
@@ -2074,6 +1683,13 @@
     <row r="47" spans="2:9" ht="19.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H39:I40"/>
+    <mergeCell ref="H41:I42"/>
+    <mergeCell ref="H43:I44"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="H3:H14"/>
+    <mergeCell ref="H15:H26"/>
+    <mergeCell ref="H27:H38"/>
     <mergeCell ref="B5:B14"/>
     <mergeCell ref="B15:B24"/>
     <mergeCell ref="B25:B34"/>
@@ -2084,13 +1700,6 @@
     <mergeCell ref="F27:F38"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="H39:I40"/>
-    <mergeCell ref="H41:I42"/>
-    <mergeCell ref="H43:I44"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="H3:H14"/>
-    <mergeCell ref="H15:H26"/>
-    <mergeCell ref="H27:H38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/bus_booking.xlsx
+++ b/bus_booking.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\front2\OneDrive\ドキュメント\bus-booking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFDAB55-9B92-4FF0-849E-B2F982AF3C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB8D2E5-4E63-430F-9AE1-3D228AAA9C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EED53E60-892A-4A6C-956D-BF49B55530D5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="print" sheetId="3" r:id="rId2"/>
+    <sheet name="print" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">print!$B$1:$D$44,print!$F$1:$I$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">print!$B$1:$D$44,print!$F$1:$I$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>月　　　　日   　　(　　　)</t>
     <rPh sb="0" eb="1">
@@ -200,7 +199,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -431,47 +430,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -597,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -616,58 +574,19 @@
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -703,10 +622,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -988,258 +934,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C007A4-FB0C-460B-8A76-612E291B3C94}">
-  <dimension ref="B1:D44"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="1" max="1" width="3.25" customWidth="1"/>
-    <col min="3" max="4" width="42.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:4" ht="24">
-      <c r="D1" s="8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" ht="9.75" customHeight="1" thickBot="1">
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="2:4" ht="24.95" customHeight="1">
-      <c r="B3" s="9"/>
-      <c r="C3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="10.5" customHeight="1">
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="23">
-        <v>0.25347222222222221</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6" s="23"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" s="23"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" s="23"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" s="23"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10" s="23"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" s="23"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12" s="23"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" s="23"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" s="23"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" s="23">
-        <v>0.2638888888888889</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" s="23"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="23"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="23"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" s="23"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="23"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" s="23"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" s="23"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-    </row>
-    <row r="23" spans="2:4">
-      <c r="B23" s="23"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" s="23"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20"/>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" s="23">
-        <v>0.27777777777777779</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="23"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27" s="23"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" s="23"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" s="23"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" s="23"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" s="23"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" s="23"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="23"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="23"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="20"/>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="23">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="23"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" s="23"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="23"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18"/>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="23"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="18"/>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" s="23"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="18"/>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="23"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="18"/>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" s="23"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="18"/>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="23"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="18"/>
-    </row>
-    <row r="44" spans="2:4" ht="19.5" thickBot="1">
-      <c r="B44" s="24"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="22"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="B15:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B44"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF8E9232-62D3-4B7F-B723-39954B0A9115}">
   <dimension ref="B1:I47"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1267,429 +961,422 @@
     </row>
     <row r="3" spans="2:9" ht="24" customHeight="1">
       <c r="B3" s="9"/>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="37" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="4"/>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="32" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B4" s="12"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="33"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="42"/>
+      <c r="F4" s="37"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="45"/>
+      <c r="H4" s="32"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B5" s="23">
+      <c r="B5" s="19">
         <v>0.25347222222222221</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="F5" s="28"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="12"/>
+      <c r="F5" s="37"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="45"/>
+      <c r="H5" s="32"/>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B6" s="23"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-      <c r="F6" s="28"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="45"/>
+      <c r="H6" s="32"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B7" s="23"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
-      <c r="F7" s="28"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="F7" s="37"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="45"/>
+      <c r="H7" s="32"/>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B8" s="23"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="F8" s="28"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="F8" s="37"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="45"/>
+      <c r="H8" s="32"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B9" s="23"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
-      <c r="F9" s="28"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="14"/>
+      <c r="F9" s="37"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="45"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B10" s="23"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-      <c r="F10" s="28"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="F10" s="37"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="45"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B11" s="23"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
-      <c r="F11" s="28"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="14"/>
+      <c r="F11" s="37"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="45"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B12" s="23"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18"/>
-      <c r="F12" s="28"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="F12" s="37"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="45"/>
+      <c r="H12" s="32"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B13" s="23"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="F13" s="28"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14"/>
+      <c r="F13" s="37"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="45"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B14" s="23"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B15" s="23">
+      <c r="B15" s="19">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="F15" s="28" t="s">
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="F15" s="37" t="s">
         <v>3</v>
       </c>
       <c r="G15" s="4"/>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="32" t="s">
         <v>4</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B16" s="23"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="F16" s="28"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
+      <c r="F16" s="37"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="45"/>
+      <c r="H16" s="32"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B17" s="23"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="F17" s="28"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="14"/>
+      <c r="F17" s="37"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="45"/>
+      <c r="H17" s="32"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B18" s="23"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="F18" s="28"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="F18" s="37"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="45"/>
+      <c r="H18" s="32"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B19" s="23"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="F19" s="28"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="F19" s="37"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="45"/>
+      <c r="H19" s="32"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B20" s="23"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="F20" s="37"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="45"/>
+      <c r="H20" s="32"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B21" s="23"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-      <c r="F21" s="28"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="F21" s="37"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="45"/>
+      <c r="H21" s="32"/>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B22" s="23"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-      <c r="F22" s="28"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="F22" s="37"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="45"/>
+      <c r="H22" s="32"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B23" s="23"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="F23" s="28"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="14"/>
+      <c r="F23" s="37"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="45"/>
+      <c r="H23" s="32"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B24" s="23"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20"/>
-      <c r="F24" s="28"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="F24" s="37"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="45"/>
+      <c r="H24" s="32"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B25" s="23">
+      <c r="B25" s="19">
         <v>0.27777777777777779</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
-      <c r="F25" s="28"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="F25" s="37"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="45"/>
+      <c r="H25" s="32"/>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B26" s="23"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B27" s="23"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="F27" s="29" t="s">
+      <c r="B27" s="19"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="F27" s="38" t="s">
         <v>14</v>
       </c>
       <c r="G27" s="4"/>
-      <c r="H27" s="46" t="s">
+      <c r="H27" s="33" t="s">
         <v>5</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B28" s="23"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="F28" s="29"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="F28" s="38"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="46"/>
+      <c r="H28" s="33"/>
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B29" s="23"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-      <c r="F29" s="29"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="14"/>
+      <c r="F29" s="38"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="46"/>
+      <c r="H29" s="33"/>
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B30" s="23"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="F30" s="29"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="F30" s="38"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="46"/>
+      <c r="H30" s="33"/>
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B31" s="23"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="F31" s="29"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="F31" s="38"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="46"/>
+      <c r="H31" s="33"/>
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B32" s="23"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="F32" s="29"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
+      <c r="F32" s="38"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="46"/>
+      <c r="H32" s="33"/>
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B33" s="23"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="F33" s="29"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="14"/>
+      <c r="F33" s="38"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="46"/>
+      <c r="H33" s="33"/>
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B34" s="23"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="20"/>
-      <c r="F34" s="29"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="16"/>
+      <c r="F34" s="38"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="46"/>
+      <c r="H34" s="33"/>
       <c r="I34" s="5"/>
     </row>
     <row r="35" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B35" s="23">
+      <c r="B35" s="19">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
-      <c r="F35" s="29"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="F35" s="38"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="46"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="5"/>
     </row>
     <row r="36" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B36" s="23"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="F36" s="29"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14"/>
+      <c r="F36" s="38"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="46"/>
+      <c r="H36" s="33"/>
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B37" s="23"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
-      <c r="F37" s="29"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="14"/>
+      <c r="F37" s="38"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="46"/>
+      <c r="H37" s="33"/>
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="23"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="46"/>
-      <c r="I38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="14"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="15"/>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="23"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="18"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="44" t="s">
+      <c r="B39" s="19"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H39" s="34" t="s">
+      <c r="H39" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I39" s="35"/>
+      <c r="I39" s="22"/>
     </row>
     <row r="40" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B40" s="23"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="18"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="37"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="14"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B41" s="23"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="18"/>
-      <c r="F41" s="26"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="14"/>
+      <c r="F41" s="35"/>
       <c r="G41" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H41" s="38" t="s">
+      <c r="H41" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I41" s="39"/>
+      <c r="I41" s="26"/>
     </row>
     <row r="42" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B42" s="23"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="18"/>
-      <c r="F42" s="26"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="14"/>
+      <c r="F42" s="35"/>
       <c r="G42" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H42" s="40"/>
-      <c r="I42" s="41"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="28"/>
     </row>
     <row r="43" spans="2:9" ht="18.75" customHeight="1">
-      <c r="B43" s="23"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="18"/>
-      <c r="F43" s="26"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="14"/>
+      <c r="F43" s="35"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="40" t="s">
+      <c r="H43" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="I43" s="41"/>
+      <c r="I43" s="28"/>
     </row>
     <row r="44" spans="2:9" ht="19.5" thickBot="1">
-      <c r="B44" s="24"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="22"/>
-      <c r="F44" s="27"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="18"/>
+      <c r="F44" s="36"/>
       <c r="G44" s="7"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="43"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="30"/>
     </row>
     <row r="46" spans="2:9" ht="18.75" customHeight="1"/>
     <row r="47" spans="2:9" ht="19.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="H39:I40"/>
-    <mergeCell ref="H41:I42"/>
-    <mergeCell ref="H43:I44"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="H3:H14"/>
-    <mergeCell ref="H15:H26"/>
-    <mergeCell ref="H27:H38"/>
     <mergeCell ref="B5:B14"/>
     <mergeCell ref="B15:B24"/>
     <mergeCell ref="B25:B34"/>
@@ -1700,6 +1387,13 @@
     <mergeCell ref="F27:F38"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="H39:I40"/>
+    <mergeCell ref="H41:I42"/>
+    <mergeCell ref="H43:I44"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="H3:H14"/>
+    <mergeCell ref="H15:H26"/>
+    <mergeCell ref="H27:H38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
